--- a/dist/assets/BOs/Tsukuyomi.xlsx
+++ b/dist/assets/BOs/Tsukuyomi.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chris\OneDrive\Github\DoD\DeitiesOfDeath\public\assets\BOs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\doc\coding\DoD\DeitiesOfDeath\public\assets\BOs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FEF327E-6852-43EC-88B5-85CC6679B1D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DBBFC63-1506-435A-B71E-C87505B27A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8160" yWindow="6630" windowWidth="43200" windowHeight="23445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -27,9 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
   <si>
-    <t>Tsukyomi - Rush into 2TC - Husksuppe</t>
-  </si>
-  <si>
     <t>Archaic</t>
   </si>
   <si>
@@ -303,6 +300,9 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=1cG3tcC4cio</t>
+  </si>
+  <si>
+    <t>Rush into 2TC - Husksuppe</t>
   </si>
 </sst>
 </file>
@@ -487,7 +487,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -767,182 +767,182 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
       <c r="D1" s="8"/>
     </row>
-    <row r="2" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
       <c r="D2" s="11"/>
     </row>
-    <row r="3" spans="1:4" ht="58.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="56.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" spans="1:4" ht="101.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="97.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:4" ht="97.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="115.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:4" ht="58.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="56.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="56.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="58.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" spans="1:4" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
       <c r="D8" s="11"/>
     </row>
-    <row r="9" spans="1:4" ht="58.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="56.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="1:4" ht="87" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="84" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="9" t="s">
         <v>17</v>
-      </c>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
-        <v>18</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
       <c r="D11" s="11"/>
     </row>
-    <row r="12" spans="1:4" ht="58.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="56.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" ht="87" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="84" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="1" t="s">
+    </row>
+    <row r="14" spans="1:4" ht="125.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="129.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="B14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="1" t="s">
+    </row>
+    <row r="15" spans="1:4" ht="97.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" ht="101.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="B15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="D15" s="2"/>
     </row>
-    <row r="16" spans="1:4" ht="58.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="56.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2"/>
       <c r="B16" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
     </row>
-    <row r="17" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
     </row>
-    <row r="18" spans="1:4" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="87" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>29</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>30</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
